--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45967.375</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45967.49652777778</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.49652777778</v>
       </c>
     </row>
     <row r="12">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.625</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.75</v>
       </c>
     </row>
     <row r="19">

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK22"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.625</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.75</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.625</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="M20" t="n">
         <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.875</v>
+        <v>45967.75</v>
       </c>
     </row>
     <row r="22">
@@ -3208,126 +3208,771 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>45967.8125</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45967.83333333334</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45967.875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45967.875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
+        <v>45967.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
+      <c r="L27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N27" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK27"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="4">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="5">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45967.49652777778</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.49652777778</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.625</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45967.625</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.75</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.75</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
         <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.96</v>
+        <v>2.94</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.83333333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,16 +3411,16 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.875</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,393 +3586,6 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45967.875</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>FC Dallas</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
-        <v>45967.875</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
-        <v>45967.875</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.49652777778</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45967.49652777778</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.625</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.625</v>
+        <v>45967.75</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="M19" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>3.96</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.75</v>
+        <v>45967.83333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.875</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.94</v>
+        <v>8.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,264 +3328,6 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.83333333334</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Australia A-League</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Brisbane Roar</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Newcastle Jets FC</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>45967.875</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK22"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="4">
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="5">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45967.49652777778</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.49652777778</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.625</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.75</v>
+        <v>45967.625</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="M19" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N19" t="n">
-        <v>3.96</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.75</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.875</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="22">
@@ -3208,126 +3208,384 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>45967.83333333334</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45967.875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="L24" t="n">
         <v>1.4</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M24" t="n">
         <v>4.6</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N24" t="n">
         <v>8.5</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="Z24" t="n">
         <v>2.02</v>
       </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.375</v>
       </c>
     </row>
     <row r="4">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="6">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45967.49652777778</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.49652777778</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="18">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.625</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.75</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N22" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45967.875</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="24">
@@ -3466,126 +3466,384 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45967.83333333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45967.875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>1.4</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>4.6</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>8.5</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z26" t="n">
         <v>2.02</v>
       </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45967.375</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="4">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.49652777778</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45967.49652777778</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.625</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.75</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.83333333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.875</v>
       </c>
     </row>
     <row r="24">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
-        <v>2.94</v>
+        <v>8.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,264 +3586,6 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45967.83333333334</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Australia A-League</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Brisbane Roar</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Newcastle Jets FC</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
-        <v>45967.875</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="6">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="7">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45967.49652777778</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.49652777778</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.625</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.75</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N22" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45967.875</v>
+        <v>45967.75</v>
       </c>
     </row>
     <row r="24">
@@ -3466,126 +3466,513 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45967.8125</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45967.83333333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
+        <v>45967.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L27" t="n">
         <v>1.4</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M27" t="n">
         <v>4.6</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N27" t="n">
         <v>8.5</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z27" t="n">
         <v>2.02</v>
       </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK27"/>
+  <dimension ref="A1:AK28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3853,126 +3853,255 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3" t="n">
+        <v>45967.875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="3" t="n">
+      <c r="L28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK28"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.625</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.83333333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45967.75</v>
+        <v>45967.875</v>
       </c>
     </row>
     <row r="24">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.96</v>
+        <v>7.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,522 +3586,6 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45967.8125</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
-        <v>45967.83333333334</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Australia A-League</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Brisbane Roar</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Newcastle Jets FC</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
-        <v>45967.875</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="3" t="n">
-        <v>45967.875</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.85</v>
+        <v>4.28</v>
       </c>
       <c r="M2" t="n">
         <v>3.65</v>
@@ -681,65 +681,65 @@
         <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.2</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.14</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3000,7 +3000,7 @@
         <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
@@ -3012,10 +3012,10 @@
         <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
         <v>1.33</v>
@@ -3024,7 +3024,7 @@
         <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X20" t="n">
         <v>3.1</v>
@@ -3036,7 +3036,7 @@
         <v>1.63</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AB20" t="n">
         <v>1.25</v>
@@ -3129,34 +3129,34 @@
         <v>3.96</v>
       </c>
       <c r="O21" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
         <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="Y21" t="n">
         <v>2.25</v>
@@ -3165,10 +3165,10 @@
         <v>1.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AC21" t="n">
         <v>1.95</v>
@@ -3190,7 +3190,7 @@
         <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3261,10 +3261,10 @@
         <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
         <v>1.47</v>
@@ -3279,7 +3279,7 @@
         <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
         <v>1.55</v>
@@ -3288,22 +3288,22 @@
         <v>2.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AA22" t="n">
         <v>4.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
         <v>1.58</v>
@@ -3516,19 +3516,19 @@
         <v>7.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P24" t="n">
         <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="T24" t="n">
         <v>2.55</v>
@@ -3543,7 +3543,7 @@
         <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y24" t="n">
         <v>1.72</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.28</v>
+        <v>3.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P2" t="n">
         <v>2.37</v>
@@ -690,34 +690,34 @@
         <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="T2" t="n">
         <v>2.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC2" t="n">
         <v>1.68</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.07</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Q16" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
       </c>
       <c r="S16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.75</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
         <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X16" t="n">
         <v>3.95</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.33</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.91</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.74</v>
+        <v>5.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>3.45</v>
+        <v>4.28</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.72</v>
+        <v>2.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>2.68</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.4</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="X19" t="n">
-        <v>4.35</v>
+        <v>2.97</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.62</v>
+        <v>2.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
         <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W20" t="n">
         <v>1.33</v>
@@ -3030,16 +3030,16 @@
         <v>3.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AA20" t="n">
         <v>3.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC20" t="n">
         <v>1.85</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3120,55 +3120,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="M21" t="n">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="N21" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X21" t="n">
         <v>2.9</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.76</v>
-      </c>
       <c r="Y21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AC21" t="n">
         <v>1.95</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3261,49 +3261,49 @@
         <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>4.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
         <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="X22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y22" t="n">
         <v>2.45</v>
       </c>
-      <c r="Y22" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Z22" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC22" t="n">
         <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3507,34 +3507,34 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>7.2</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
         <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
         <v>1.04</v>
@@ -3543,25 +3543,25 @@
         <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
         <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>4.45</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="P18" t="n">
-        <v>2.59</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="X18" t="n">
-        <v>4.28</v>
+        <v>2.97</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.68</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.95</v>
+        <v>1.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="X19" t="n">
-        <v>2.97</v>
+        <v>4.28</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.13</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.55</v>
+        <v>2.68</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3135,16 +3135,16 @@
         <v>2.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
         <v>2.74</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
         <v>1.32</v>
@@ -3156,7 +3156,7 @@
         <v>1.4</v>
       </c>
       <c r="X21" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="Y21" t="n">
         <v>2.2</v>
@@ -3165,13 +3165,13 @@
         <v>1.66</v>
       </c>
       <c r="AA21" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AD21" t="n">
         <v>1.75</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3264,22 +3264,22 @@
         <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.08</v>
+        <v>3.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T22" t="n">
         <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W22" t="n">
         <v>1.4</v>
@@ -3288,22 +3288,22 @@
         <v>2.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC22" t="n">
         <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3507,16 +3507,16 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="N24" t="n">
-        <v>8.550000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="O24" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
@@ -3525,19 +3525,19 @@
         <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="T24" t="n">
         <v>2.59</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
@@ -3546,16 +3546,16 @@
         <v>3.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AA24" t="n">
         <v>2.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
         <v>1.95</v>
@@ -3577,7 +3577,7 @@
         <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="O2" t="n">
         <v>4.5</v>
@@ -684,7 +684,7 @@
         <v>2.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="R2" t="n">
         <v>1.32</v>
@@ -699,16 +699,16 @@
         <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
         <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Z2" t="n">
         <v>1.97</v>
@@ -717,13 +717,13 @@
         <v>2.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.09</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2991,19 +2991,19 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="M20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O20" t="n">
         <v>3.2</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
         <v>3.2</v>
@@ -3012,13 +3012,13 @@
         <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
         <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
         <v>1.08</v>
@@ -3027,16 +3027,16 @@
         <v>1.33</v>
       </c>
       <c r="X20" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="AB20" t="n">
         <v>1.2</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,19 +672,19 @@
         <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="N2" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="O2" t="n">
         <v>4.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.32</v>
@@ -693,19 +693,19 @@
         <v>2.92</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="U2" t="n">
         <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="Y2" t="n">
         <v>1.75</v>
@@ -714,10 +714,10 @@
         <v>1.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC2" t="n">
         <v>1.67</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="M16" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.9</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.14</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.51041666666</v>
       </c>
     </row>
     <row r="19">
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
         <v>4.45</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>6.14</v>
       </c>
       <c r="O19" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>6.31</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
@@ -2886,7 +2886,7 @@
         <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
         <v>1.49</v>
@@ -2895,25 +2895,25 @@
         <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X19" t="n">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
         <v>2.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
         <v>1.91</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="M20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.96</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y20" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Z20" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AA20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="M21" t="n">
-        <v>3.42</v>
+        <v>2.96</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,55 +3249,55 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
         <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>2.94</v>
+        <v>3.96</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.88</v>
+        <v>4.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X22" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
         <v>1.95</v>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="N23" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45967.875</v>
+        <v>45967.83333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,126 +3466,255 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45967.875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N24" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="L25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>7</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="Q25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R25" t="n">
         <v>1.33</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>3.04</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>2.59</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>1.44</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="V25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.25</v>
       </c>
-      <c r="X24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="X25" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
+      <c r="AC25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="O2" t="n">
         <v>4.5</v>
@@ -684,7 +684,7 @@
         <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
         <v>1.32</v>
@@ -693,31 +693,31 @@
         <v>2.92</v>
       </c>
       <c r="T2" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U2" t="n">
         <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="Y2" t="n">
         <v>1.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>1.67</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.09</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,62 +2862,62 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>2.27</v>
       </c>
       <c r="M19" t="n">
-        <v>4.45</v>
+        <v>3.14</v>
       </c>
       <c r="N19" t="n">
-        <v>6.14</v>
+        <v>2.93</v>
       </c>
       <c r="O19" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.9</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.6</v>
+        <v>1.52</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.14</v>
+        <v>4.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.93</v>
+        <v>6.14</v>
       </c>
       <c r="O20" t="n">
-        <v>2.97</v>
+        <v>1.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.76</v>
+        <v>6.31</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X20" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.52</v>
+        <v>2.6</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3129,10 +3129,10 @@
         <v>2.56</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
         <v>3.2</v>
@@ -3144,19 +3144,19 @@
         <v>2.56</v>
       </c>
       <c r="T21" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="U21" t="n">
         <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X21" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
         <v>2.15</v>
@@ -3165,10 +3165,10 @@
         <v>1.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC21" t="n">
         <v>1.85</v>
@@ -3258,7 +3258,7 @@
         <v>3.96</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="P22" t="n">
         <v>2.1</v>
@@ -3267,25 +3267,25 @@
         <v>4.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
         <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>3.04</v>
+        <v>3.29</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="Y22" t="n">
         <v>2.25</v>
@@ -3294,16 +3294,16 @@
         <v>1.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AC22" t="n">
         <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3387,28 +3387,28 @@
         <v>2.94</v>
       </c>
       <c r="O23" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
         <v>2.42</v>
       </c>
       <c r="T23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W23" t="n">
         <v>1.55</v>
@@ -3423,16 +3423,16 @@
         <v>1.46</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3648,10 +3648,10 @@
         <v>1.83</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="R25" t="n">
         <v>1.33</v>
@@ -3666,13 +3666,13 @@
         <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
         <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="Y25" t="n">
         <v>1.72</v>
@@ -3681,16 +3681,16 @@
         <v>2</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,10 +672,10 @@
         <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="O2" t="n">
         <v>4.5</v>
@@ -684,37 +684,37 @@
         <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
         <v>2.45</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="V2" t="n">
         <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AB2" t="n">
         <v>1.36</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="n">
         <v>1.14</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="8">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.49652777778</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.49652777778</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.51041666666</v>
+        <v>45967.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.51041666666</v>
       </c>
     </row>
     <row r="20">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
         <v>4.45</v>
@@ -3003,37 +3003,37 @@
         <v>1.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.31</v>
+        <v>5.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA20" t="n">
         <v>2.5</v>
@@ -3045,7 +3045,7 @@
         <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.42</v>
+        <v>2.79</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="U21" t="n">
         <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.88</v>
+        <v>3.58</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>2.65</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.96</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
         <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T22" t="n">
-        <v>3.29</v>
+        <v>3.21</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X22" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AB22" t="n">
         <v>1.24</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y23" t="n">
         <v>2.2</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Z23" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
         <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="N24" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45967.875</v>
+        <v>45967.83333333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,126 +3595,255 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45967.875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="L26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>8</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.34</v>
       </c>
-      <c r="Q25" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="R25" t="n">
+      <c r="Q26" t="n">
+        <v>7</v>
+      </c>
+      <c r="R26" t="n">
         <v>1.33</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="S26" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.59</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>1.44</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>1.03</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="W26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X26" t="n">
         <v>3.62</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="Y26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.85</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AB26" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD25" t="n">
+      <c r="AC26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.68</v>
       </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.5</v>
+        <v>45967.51041666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45967.51041666666</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="U21" t="n">
         <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X21" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>4.51</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="AB22" t="n">
         <v>1.24</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="23">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.25</v>
       </c>
-      <c r="N23" t="n">
-        <v>4</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.29</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="X23" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC23" t="n">
         <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.83333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z24" t="n">
         <v>2.2</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AA24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.875</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.36</v>
+        <v>1.32</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>4.79</v>
       </c>
       <c r="N25" t="n">
-        <v>2.75</v>
+        <v>7.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,135 +3715,6 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45967.875</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N26" t="n">
-        <v>8</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>7</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45967.41666666666</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="6">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,19 +2542,19 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.49652777778</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45967.49652777778</v>
+        <v>45967.51041666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.51041666666</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2862,16 +2862,16 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
@@ -2880,7 +2880,7 @@
         <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
         <v>2.62</v>
@@ -2889,13 +2889,13 @@
         <v>3.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X19" t="n">
         <v>2.9</v>
@@ -2907,7 +2907,7 @@
         <v>1.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.58</v>
+        <v>3.71</v>
       </c>
       <c r="AB19" t="n">
         <v>1.22</v>
@@ -2916,7 +2916,7 @@
         <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,77 +2991,77 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.4</v>
+        <v>2.56</v>
       </c>
       <c r="M20" t="n">
-        <v>4.45</v>
+        <v>2.96</v>
       </c>
       <c r="N20" t="n">
-        <v>6.14</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>2.61</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>3.02</v>
       </c>
       <c r="R20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.27</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.62</v>
+        <v>1.39</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,78 +3120,78 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>4.51</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.92</v>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="O22" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.51</v>
+        <v>3.95</v>
       </c>
       <c r="R22" t="n">
         <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T22" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="X22" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA22" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.83333333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2.2</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AA23" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.875</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.32</v>
+        <v>1.32</v>
       </c>
       <c r="M24" t="n">
-        <v>3.56</v>
+        <v>4.79</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>7.5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,135 +3586,6 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45967.875</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="N25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,52 +669,52 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
         <v>2.45</v>
       </c>
       <c r="U2" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
         <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="Y2" t="n">
         <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AB2" t="n">
         <v>1.36</v>
@@ -723,7 +723,7 @@
         <v>1.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45967.22916666666</v>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.05</v>
+        <v>7.5</v>
       </c>
       <c r="M3" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45967.41666666666</v>
+        <v>45967.40972222222</v>
       </c>
     </row>
     <row r="4">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45967.45833333334</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="8">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,19 +2542,19 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45967.49652777778</v>
+        <v>45967.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45967.51041666666</v>
+        <v>45967.49652777778</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45967.60416666666</v>
+        <v>45967.51041666666</v>
       </c>
     </row>
     <row r="19">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.01</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.02</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.04</v>
+        <v>1.59</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.71</v>
+        <v>2.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.66</v>
+        <v>2.57</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.56</v>
+        <v>2.01</v>
       </c>
       <c r="M20" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
         <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="U20" t="n">
         <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W20" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X20" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="O21" t="n">
-        <v>2.54</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.51</v>
+        <v>3.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="T21" t="n">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="U21" t="n">
         <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X21" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.92</v>
+        <v>1.39</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
         <v>3.08</v>
       </c>
       <c r="N22" t="n">
-        <v>2.94</v>
+        <v>3.96</v>
       </c>
       <c r="O22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T22" t="n">
         <v>3.1</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.56</v>
+        <v>3.08</v>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45967.875</v>
+        <v>45967.83333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,126 +3466,255 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45967.875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="L25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.35</v>
       </c>
-      <c r="AC24" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AC25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.16</v>
       </c>
-      <c r="AH24" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
+      <c r="AH25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,115 +508,60 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under25</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over35</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under35</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_Yes</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_No</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>homeGoals</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_A_D</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -678,76 +623,39 @@
         <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>4.85</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ2" t="n">
         <v>1.57</v>
       </c>
-      <c r="AK2" s="3" t="n">
+      <c r="Z2" s="3" t="n">
         <v>45967.22916666666</v>
       </c>
     </row>
@@ -816,10 +724,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -837,46 +745,9 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3" t="n">
         <v>45967.40972222222</v>
       </c>
     </row>
@@ -968,44 +839,7 @@
       <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="3" t="n">
+      <c r="Z4" s="3" t="n">
         <v>45967.41666666666</v>
       </c>
     </row>
@@ -1097,44 +931,7 @@
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="3" t="n">
+      <c r="Z5" s="3" t="n">
         <v>45967.41666666666</v>
       </c>
     </row>
@@ -1226,44 +1023,7 @@
       <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
+      <c r="Z6" s="3" t="n">
         <v>45967.4375</v>
       </c>
     </row>
@@ -1355,44 +1115,7 @@
       <c r="Y7" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="3" t="n">
+      <c r="Z7" s="3" t="n">
         <v>45967.4375</v>
       </c>
     </row>
@@ -1484,44 +1207,7 @@
       <c r="Y8" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="3" t="n">
+      <c r="Z8" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1613,44 +1299,7 @@
       <c r="Y9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="3" t="n">
+      <c r="Z9" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1742,44 +1391,7 @@
       <c r="Y10" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="n">
+      <c r="Z10" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1871,44 +1483,7 @@
       <c r="Y11" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="3" t="n">
+      <c r="Z11" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -2000,44 +1575,7 @@
       <c r="Y12" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="3" t="n">
+      <c r="Z12" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -2129,44 +1667,7 @@
       <c r="Y13" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="3" t="n">
+      <c r="Z13" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -2258,44 +1759,7 @@
       <c r="Y14" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
+      <c r="Z14" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -2387,44 +1851,7 @@
       <c r="Y15" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
+      <c r="Z15" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -2516,44 +1943,7 @@
       <c r="Y16" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="3" t="n">
+      <c r="Z16" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -2613,76 +2003,39 @@
         <v>2.06</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>1.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="U17" t="n">
-        <v>1.43</v>
+        <v>2.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="X17" t="n">
-        <v>3.58</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ17" t="n">
         <v>1.72</v>
       </c>
-      <c r="AK17" s="3" t="n">
+      <c r="Z17" s="3" t="n">
         <v>45967.49652777778</v>
       </c>
     </row>
@@ -2774,44 +2127,7 @@
       <c r="Y18" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
+      <c r="Z18" s="3" t="n">
         <v>45967.51041666666</v>
       </c>
     </row>
@@ -2871,76 +2187,39 @@
         <v>6.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>1.54</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>2.57</v>
       </c>
       <c r="X19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="3" t="n">
         <v>45967.60416666666</v>
       </c>
     </row>
@@ -3000,76 +2279,39 @@
         <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>3.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>1.32</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>1.67</v>
       </c>
       <c r="T20" t="n">
-        <v>3.02</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.86</v>
       </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="W20" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="X20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3" t="n">
         <v>45967.60416666666</v>
       </c>
     </row>
@@ -3129,76 +2371,39 @@
         <v>2.56</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>1.42</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>3.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.02</v>
+        <v>1.32</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>2.15</v>
       </c>
       <c r="S21" t="n">
-        <v>2.58</v>
+        <v>1.63</v>
       </c>
       <c r="T21" t="n">
-        <v>3.21</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X21" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>45967.70833333334</v>
       </c>
     </row>
@@ -3258,76 +2463,39 @@
         <v>3.96</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>3.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.37</v>
+        <v>1.32</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>1.65</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.74</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="X22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="n">
         <v>45967.8125</v>
       </c>
     </row>
@@ -3387,76 +2555,39 @@
         <v>2.94</v>
       </c>
       <c r="O23" t="n">
-        <v>2.97</v>
+        <v>1.47</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>1.27</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="V23" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3" t="n">
         <v>45967.83333333334</v>
       </c>
     </row>
@@ -3525,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -3546,46 +2677,9 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3" t="n">
         <v>45967.875</v>
       </c>
     </row>
@@ -3645,76 +2739,39 @@
         <v>7.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>1.42</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="S25" t="n">
-        <v>3.14</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>1.26</v>
+        <v>2.72</v>
       </c>
       <c r="X25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,60 +508,75 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Odd_H_HT</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_D_HT</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_A_HT</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_marcar_prim_H</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_marcar_prim_A</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -623,39 +638,48 @@
         <v>1.68</v>
       </c>
       <c r="O2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.33</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>1.42</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>1.73</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>2</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
         <v>1.67</v>
       </c>
-      <c r="U2" t="n">
+      <c r="X2" t="n">
         <v>2.02</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Y2" t="n">
         <v>1.22</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Z2" t="n">
         <v>1.09</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AA2" t="n">
         <v>2.6</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z2" s="3" t="n">
+      <c r="AC2" s="3" t="n">
         <v>45967.22916666666</v>
       </c>
     </row>
@@ -724,20 +748,20 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.88</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>1.8</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
@@ -747,7 +771,16 @@
       <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="3" t="n">
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="3" t="n">
         <v>45967.40972222222</v>
       </c>
     </row>
@@ -839,7 +872,16 @@
       <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="3" t="n">
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="3" t="n">
         <v>45967.41666666666</v>
       </c>
     </row>
@@ -931,7 +973,16 @@
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="3" t="n">
         <v>45967.41666666666</v>
       </c>
     </row>
@@ -1023,7 +1074,16 @@
       <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="3" t="n">
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3" t="n">
         <v>45967.4375</v>
       </c>
     </row>
@@ -1115,7 +1175,16 @@
       <c r="Y7" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="3" t="n">
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3" t="n">
         <v>45967.4375</v>
       </c>
     </row>
@@ -1207,7 +1276,16 @@
       <c r="Y8" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1299,7 +1377,16 @@
       <c r="Y9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="3" t="n">
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1391,7 +1478,16 @@
       <c r="Y10" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="3" t="n">
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1483,7 +1579,16 @@
       <c r="Y11" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="3" t="n">
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1575,7 +1680,16 @@
       <c r="Y12" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="3" t="n">
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1667,7 +1781,16 @@
       <c r="Y13" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1759,7 +1882,16 @@
       <c r="Y14" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="n">
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1851,7 +1983,16 @@
       <c r="Y15" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="n">
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -1943,7 +2084,16 @@
       <c r="Y16" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="3" t="n">
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="3" t="n">
         <v>45967.45833333334</v>
       </c>
     </row>
@@ -2003,39 +2153,48 @@
         <v>2.06</v>
       </c>
       <c r="O17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.33</v>
       </c>
-      <c r="P17" t="n">
+      <c r="S17" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="T17" t="n">
         <v>1.43</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
         <v>1.75</v>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="W17" t="n">
         <v>1.65</v>
       </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
         <v>2.11</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
         <v>1.23</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Z17" t="n">
         <v>1.27</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AA17" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z17" s="3" t="n">
+      <c r="AC17" s="3" t="n">
         <v>45967.49652777778</v>
       </c>
     </row>
@@ -2127,7 +2286,16 @@
       <c r="Y18" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="3" t="n">
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3" t="n">
         <v>45967.51041666666</v>
       </c>
     </row>
@@ -2187,39 +2355,48 @@
         <v>6.5</v>
       </c>
       <c r="O19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.29</v>
       </c>
-      <c r="P19" t="n">
+      <c r="S19" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="T19" t="n">
         <v>1.54</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>1.59</v>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>2.1</v>
       </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
         <v>1.81</v>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
         <v>1.95</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
         <v>1.09</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Z19" t="n">
         <v>2.57</v>
       </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="3" t="n">
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="3" t="n">
         <v>45967.60416666666</v>
       </c>
     </row>
@@ -2279,39 +2456,48 @@
         <v>3.5</v>
       </c>
       <c r="O20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.42</v>
       </c>
-      <c r="P20" t="n">
+      <c r="S20" t="n">
         <v>3.02</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="T20" t="n">
         <v>1.32</v>
       </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
         <v>2.04</v>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
         <v>1.67</v>
       </c>
-      <c r="T20" t="n">
+      <c r="W20" t="n">
         <v>1.8</v>
       </c>
-      <c r="U20" t="n">
+      <c r="X20" t="n">
         <v>1.86</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
         <v>1.24</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
         <v>1.66</v>
       </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3" t="n">
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3" t="n">
         <v>45967.60416666666</v>
       </c>
     </row>
@@ -2371,39 +2557,48 @@
         <v>2.56</v>
       </c>
       <c r="O21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.42</v>
       </c>
-      <c r="P21" t="n">
+      <c r="S21" t="n">
         <v>3.21</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="T21" t="n">
         <v>1.32</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>2.15</v>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>1.63</v>
       </c>
-      <c r="T21" t="n">
+      <c r="W21" t="n">
         <v>1.83</v>
       </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
         <v>1.85</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>1.27</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
         <v>1.39</v>
       </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="3" t="n">
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3" t="n">
         <v>45967.70833333334</v>
       </c>
     </row>
@@ -2463,39 +2658,48 @@
         <v>3.96</v>
       </c>
       <c r="O22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.4</v>
       </c>
-      <c r="P22" t="n">
+      <c r="S22" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="T22" t="n">
         <v>1.32</v>
       </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
         <v>2.25</v>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>1.65</v>
       </c>
-      <c r="T22" t="n">
+      <c r="W22" t="n">
         <v>2.06</v>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
         <v>1.74</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
         <v>1.3</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Z22" t="n">
         <v>1.88</v>
       </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="n">
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="n">
         <v>45967.8125</v>
       </c>
     </row>
@@ -2555,39 +2759,48 @@
         <v>2.94</v>
       </c>
       <c r="O23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.47</v>
       </c>
-      <c r="P23" t="n">
+      <c r="S23" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="T23" t="n">
         <v>1.27</v>
       </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
         <v>2.5</v>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
         <v>1.46</v>
       </c>
-      <c r="T23" t="n">
+      <c r="W23" t="n">
         <v>2</v>
       </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
         <v>1.75</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
         <v>1.32</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Z23" t="n">
         <v>1.5</v>
       </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="3" t="n">
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3" t="n">
         <v>45967.83333333334</v>
       </c>
     </row>
@@ -2656,20 +2869,20 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.66</v>
       </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
         <v>2.2</v>
       </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
@@ -2679,7 +2892,16 @@
       <c r="Y24" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="n">
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3" t="n">
         <v>45967.875</v>
       </c>
     </row>
@@ -2739,39 +2961,48 @@
         <v>7.2</v>
       </c>
       <c r="O25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>7</v>
+      </c>
+      <c r="R25" t="n">
         <v>1.36</v>
       </c>
-      <c r="P25" t="n">
+      <c r="S25" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="T25" t="n">
         <v>1.42</v>
       </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
         <v>1.72</v>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" t="n">
+      <c r="W25" t="n">
         <v>2.07</v>
       </c>
-      <c r="U25" t="n">
+      <c r="X25" t="n">
         <v>1.66</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
         <v>1.16</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
         <v>2.72</v>
       </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="3" t="n">
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3" t="n">
         <v>45967.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -629,19 +629,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O2" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
         <v>2.22</v>
@@ -650,7 +650,7 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.42</v>
@@ -668,10 +668,10 @@
         <v>2.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AA2" t="n">
         <v>2.6</v>
@@ -689,12 +689,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -757,10 +757,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>45967.40972222222</v>
+        <v>45967.38541666666</v>
       </c>
     </row>
     <row r="4">
@@ -790,12 +790,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>45967.41666666666</v>
+        <v>45967.38541666666</v>
       </c>
     </row>
     <row r="5">
@@ -891,12 +891,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>7.5</v>
       </c>
       <c r="M5" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>45967.41666666666</v>
+        <v>45967.40972222222</v>
       </c>
     </row>
     <row r="6">
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>45967.4375</v>
+        <v>45967.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2548,49 +2548,49 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2.56</v>
+        <v>5.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="AC21" s="3" t="n">
-        <v>45967.70833333334</v>
+        <v>45967.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -2608,27 +2608,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2649,58 +2649,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="M22" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N22" t="n">
-        <v>3.96</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.37</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="T22" t="n">
         <v>1.32</v>
       </c>
       <c r="U22" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W22" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="X22" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" s="3" t="n">
-        <v>45967.8125</v>
+        <v>45967.70833333334</v>
       </c>
     </row>
     <row r="23">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2750,40 +2750,40 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="M23" t="n">
         <v>3.08</v>
       </c>
       <c r="N23" t="n">
-        <v>2.94</v>
+        <v>3.96</v>
       </c>
       <c r="O23" t="n">
-        <v>2.97</v>
+        <v>2.53</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="T23" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V23" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="X23" t="n">
         <v>1.75</v>
@@ -2792,7 +2792,7 @@
         <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -2801,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="AC23" s="3" t="n">
-        <v>45967.83333333334</v>
+        <v>45967.8125</v>
       </c>
     </row>
     <row r="24">
@@ -2810,27 +2810,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2851,49 +2851,49 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="U24" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="V24" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="AC24" s="3" t="n">
-        <v>45967.875</v>
+        <v>45967.83333333334</v>
       </c>
     </row>
     <row r="25">
@@ -2964,19 +2964,19 @@
         <v>1.83</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
         <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U25" t="n">
         <v>1.72</v>
@@ -2988,13 +2988,13 @@
         <v>2.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -730,55 +730,55 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="N3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AC3" s="3" t="n">
         <v>45967.38541666666</v>
@@ -834,52 +834,52 @@
         <v>3.1</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" s="3" t="n">
         <v>45967.38541666666</v>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,55 +1134,55 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC7" s="3" t="n">
         <v>45967.41666666666</v>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1342,7 +1342,7 @@
         <v>2.79</v>
       </c>
       <c r="N9" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="M17" t="n">
         <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="O17" t="n">
         <v>3.6</v>
@@ -2165,25 +2165,25 @@
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
         <v>1.43</v>
       </c>
       <c r="U17" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="W17" t="n">
         <v>1.65</v>
       </c>
       <c r="X17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
         <v>1.27</v>
@@ -2349,13 +2349,13 @@
         <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="N19" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="P19" t="n">
         <v>2.38</v>
@@ -2364,37 +2364,37 @@
         <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="T19" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="U19" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="X19" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.57</v>
+        <v>2.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC19" s="3" t="n">
         <v>45967.60416666666</v>
@@ -2447,55 +2447,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="T20" t="n">
         <v>1.32</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.8</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" s="3" t="n">
         <v>45967.60416666666</v>
@@ -2548,55 +2548,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="U21" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.57</v>
       </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AC21" s="3" t="n">
         <v>45967.66666666666</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -629,49 +629,49 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>5.08</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
         <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U2" t="n">
         <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W2" t="n">
         <v>1.67</v>
       </c>
       <c r="X2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AA2" t="n">
         <v>2.6</v>
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -730,55 +730,55 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>2.37</v>
       </c>
       <c r="O3" t="n">
-        <v>1.65</v>
+        <v>4.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.3</v>
+        <v>3.27</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>2.71</v>
+        <v>4.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.05</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5.75</v>
       </c>
       <c r="AC3" s="3" t="n">
         <v>45967.38541666666</v>
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -831,55 +831,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.37</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.24</v>
+        <v>1.65</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>2.36</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.27</v>
+        <v>12.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>4.05</v>
+        <v>2.71</v>
       </c>
       <c r="T4" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="U4" t="n">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.31</v>
+        <v>2.79</v>
       </c>
       <c r="X4" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.28</v>
+        <v>3.92</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>1.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>5.75</v>
       </c>
       <c r="AC4" s="3" t="n">
         <v>45967.38541666666</v>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1033,55 +1033,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>45967.41666666666</v>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,55 +1134,55 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="3" t="n">
         <v>45967.41666666666</v>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2346,55 +2346,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="M19" t="n">
-        <v>4.45</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>6.1</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>1.87</v>
+        <v>2.79</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.35</v>
+        <v>2.96</v>
       </c>
       <c r="T19" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="V19" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="W19" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X19" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.72</v>
+        <v>1.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" s="3" t="n">
         <v>45967.60416666666</v>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2447,55 +2447,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB20" t="n">
         <v>3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.3</v>
       </c>
       <c r="AC20" s="3" t="n">
         <v>45967.60416666666</v>
@@ -2548,22 +2548,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
         <v>2.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.78</v>
+        <v>5.76</v>
       </c>
       <c r="R21" t="n">
         <v>1.49</v>
@@ -2572,25 +2572,25 @@
         <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="U21" t="n">
         <v>2.29</v>
       </c>
       <c r="V21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Y21" t="n">
         <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AA21" t="n">
         <v>1.57</v>
@@ -2649,49 +2649,49 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="M22" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="R22" t="n">
         <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="T22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="U22" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="V22" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W22" t="n">
         <v>1.86</v>
       </c>
       <c r="X22" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AA22" t="n">
         <v>2.1</v>
@@ -2750,55 +2750,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="M23" t="n">
-        <v>3.08</v>
+        <v>3.39</v>
       </c>
       <c r="N23" t="n">
-        <v>3.96</v>
+        <v>4.21</v>
       </c>
       <c r="O23" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.7</v>
+        <v>4.22</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U23" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W23" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X23" t="n">
         <v>1.75</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC23" s="3" t="n">
         <v>45967.8125</v>
@@ -2851,55 +2851,55 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="M24" t="n">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="N24" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="P24" t="n">
         <v>2.01</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>4.14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
         <v>1.27</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V24" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" s="3" t="n">
         <v>45967.83333333334</v>
@@ -2952,40 +2952,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="Q25" t="n">
         <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T25" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U25" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="V25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W25" t="n">
         <v>2</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.07</v>
       </c>
       <c r="X25" t="n">
         <v>1.73</v>
@@ -2997,10 +2997,10 @@
         <v>2.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC25" s="3" t="n">
         <v>45967.89583333334</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -730,55 +730,55 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.1</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.37</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>4.24</v>
+        <v>1.61</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.27</v>
+        <v>16.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>4.05</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="U3" t="n">
-        <v>3.25</v>
+        <v>1.82</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="W3" t="n">
-        <v>2.31</v>
+        <v>3.58</v>
       </c>
       <c r="X3" t="n">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.35</v>
+        <v>1.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>5.75</v>
       </c>
       <c r="AC3" s="3" t="n">
         <v>45967.38541666666</v>
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -831,55 +831,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.65</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.36</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.3</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="S4" t="n">
-        <v>2.71</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>2.89</v>
       </c>
       <c r="V4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.05</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>5.75</v>
       </c>
       <c r="AC4" s="3" t="n">
         <v>45967.38541666666</v>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1033,55 +1033,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>45967.41666666666</v>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,55 +1134,55 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC7" s="3" t="n">
         <v>45967.41666666666</v>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1464,10 +1464,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="O21" t="n">
         <v>2.4</v>
@@ -2575,10 +2575,10 @@
         <v>1.3</v>
       </c>
       <c r="U21" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
         <v>2.11</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -629,46 +629,46 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N2" t="n">
         <v>1.65</v>
       </c>
       <c r="O2" t="n">
-        <v>5.08</v>
+        <v>5.14</v>
       </c>
       <c r="P2" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.73</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.67</v>
-      </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
         <v>1.2</v>
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -730,55 +730,55 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.61</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.5</v>
+        <v>3.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>4.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.82</v>
+        <v>2.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.88</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>3.58</v>
+        <v>2.34</v>
       </c>
       <c r="X3" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" s="3" t="n">
         <v>45967.38541666666</v>
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -831,55 +831,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>1.57</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>2.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>12.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="U4" t="n">
-        <v>2.89</v>
+        <v>1.82</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.88</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>1.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>5.75</v>
       </c>
       <c r="AC4" s="3" t="n">
         <v>45967.38541666666</v>
@@ -1143,7 +1143,7 @@
         <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
         <v>1.8</v>
@@ -1152,7 +1152,7 @@
         <v>6.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
         <v>4.1</v>
@@ -1167,16 +1167,16 @@
         <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Y7" t="n">
         <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AA7" t="n">
         <v>1.6</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1262,10 +1262,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1464,10 +1464,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="N17" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="O17" t="n">
         <v>3.6</v>
@@ -2159,22 +2159,22 @@
         <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="T17" t="n">
         <v>1.43</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="W17" t="n">
         <v>1.65</v>
@@ -2183,10 +2183,10 @@
         <v>2.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AA17" t="n">
         <v>2.2</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2346,55 +2346,55 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V19" t="n">
         <v>2.15</v>
       </c>
-      <c r="M19" t="n">
+      <c r="W19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB19" t="n">
         <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.3</v>
       </c>
       <c r="AC19" s="3" t="n">
         <v>45967.60416666666</v>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2447,55 +2447,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>2.18</v>
       </c>
       <c r="M20" t="n">
-        <v>4.45</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>6.1</v>
+        <v>3.36</v>
       </c>
       <c r="O20" t="n">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="U20" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="X20" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.72</v>
+        <v>1.67</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" s="3" t="n">
         <v>45967.60416666666</v>
@@ -2557,13 +2557,13 @@
         <v>5.4</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.76</v>
+        <v>5.22</v>
       </c>
       <c r="R21" t="n">
         <v>1.49</v>
@@ -2572,7 +2572,7 @@
         <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="U21" t="n">
         <v>2.25</v>
@@ -2581,16 +2581,16 @@
         <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
       <c r="X21" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AA21" t="n">
         <v>1.57</v>
@@ -2649,49 +2649,49 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="N22" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
         <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
         <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="T22" t="n">
         <v>1.31</v>
       </c>
       <c r="U22" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="V22" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W22" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="X22" t="n">
         <v>1.85</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AA22" t="n">
         <v>2.1</v>
@@ -2750,46 +2750,46 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="M23" t="n">
-        <v>3.39</v>
+        <v>3.08</v>
       </c>
       <c r="N23" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4.21</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.22</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="T23" t="n">
         <v>1.34</v>
       </c>
       <c r="U23" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V23" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W23" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z23" t="n">
         <v>1.92</v>
@@ -2851,49 +2851,49 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="O24" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P24" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.14</v>
+        <v>3.68</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="U24" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="X24" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AA24" t="n">
         <v>1.9</v>
@@ -2952,49 +2952,49 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="Q25" t="n">
         <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
         <v>2.69</v>
       </c>
       <c r="T25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U25" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="V25" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="X25" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AA25" t="n">
         <v>1.38</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -612,20 +612,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1262,10 +1262,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2346,55 +2346,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="M19" t="n">
-        <v>4.55</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>6.1</v>
+        <v>3.36</v>
       </c>
       <c r="O19" t="n">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="X19" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" s="3" t="n">
         <v>45967.60416666666</v>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2447,55 +2447,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="M20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB20" t="n">
         <v>3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.3</v>
       </c>
       <c r="AC20" s="3" t="n">
         <v>45967.60416666666</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -689,12 +689,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,84 +704,84 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>7.1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W3" t="n">
         <v>2.35</v>
       </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.34</v>
-      </c>
       <c r="X3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>45967.38541666666</v>
+        <v>45967.40972222222</v>
       </c>
     </row>
     <row r="4">
@@ -790,12 +790,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -827,62 +827,62 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>2.66</v>
       </c>
       <c r="P4" t="n">
-        <v>2.54</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.5</v>
+        <v>4.65</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>3.92</v>
       </c>
       <c r="T4" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="U4" t="n">
-        <v>1.82</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.88</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="X4" t="n">
         <v>1.43</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.4</v>
+        <v>1.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>45967.38541666666</v>
+        <v>45967.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -891,12 +891,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>45967.40972222222</v>
+        <v>45967.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,16 +1007,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1029,62 +1029,62 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>45967.41666666666</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="7">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1130,62 +1130,62 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.1</v>
+        <v>3.28</v>
       </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="T7" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="U7" t="n">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.89</v>
+        <v>1.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>45967.41666666666</v>
+        <v>45967.4375</v>
       </c>
     </row>
     <row r="8">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1538,55 +1538,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC11" s="3" t="n">
         <v>45967.45833333334</v>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1736,17 +1736,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>45967.51041666666</v>
+        <v>45967.51388888889</v>
       </c>
     </row>
     <row r="19">
@@ -2548,49 +2548,49 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.22</v>
+        <v>4.31</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="U21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W21" t="n">
         <v>2.25</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.37</v>
-      </c>
       <c r="X21" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
         <v>1.57</v>
@@ -2658,22 +2658,22 @@
         <v>2.56</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
         <v>3.24</v>
       </c>
       <c r="T22" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="U22" t="n">
         <v>2.15</v>
@@ -2682,13 +2682,13 @@
         <v>1.63</v>
       </c>
       <c r="W22" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="X22" t="n">
         <v>1.85</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
         <v>1.41</v>
@@ -2759,22 +2759,22 @@
         <v>3.96</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.21</v>
+        <v>4.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="T23" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U23" t="n">
         <v>2.25</v>
@@ -2783,16 +2783,16 @@
         <v>1.65</v>
       </c>
       <c r="W23" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="X23" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AA23" t="n">
         <v>1.67</v>
@@ -2860,22 +2860,22 @@
         <v>2.94</v>
       </c>
       <c r="O24" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
         <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="U24" t="n">
         <v>2.5</v>
@@ -2884,13 +2884,13 @@
         <v>1.46</v>
       </c>
       <c r="W24" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
         <v>1.56</v>
@@ -2961,19 +2961,19 @@
         <v>7.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="P25" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="T25" t="n">
         <v>1.43</v>
@@ -2985,7 +2985,7 @@
         <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="X25" t="n">
         <v>1.75</v>
@@ -2994,7 +2994,7 @@
         <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="AA25" t="n">
         <v>1.38</v>

--- a/jogos_2025-11-06.xlsx
+++ b/jogos_2025-11-06.xlsx
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -827,59 +827,59 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="3" t="n">
         <v>45967.41666666666</v>
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -928,59 +928,59 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>45967.41666666666</v>
@@ -1007,16 +1007,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1033,55 +1033,55 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.25</v>
       </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>13</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.55</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.82</v>
+        <v>2.89</v>
       </c>
       <c r="V6" t="n">
-        <v>1.88</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.33</v>
+        <v>1.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>45967.4375</v>
@@ -1108,16 +1108,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1134,55 +1134,55 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>13</v>
       </c>
       <c r="O7" t="n">
-        <v>3.65</v>
+        <v>1.54</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>2.51</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.28</v>
+        <v>14.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.58</v>
+        <v>2.32</v>
       </c>
       <c r="T7" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.89</v>
+        <v>1.82</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.88</v>
       </c>
       <c r="W7" t="n">
-        <v>2.06</v>
+        <v>2.79</v>
       </c>
       <c r="X7" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.28</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>1.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>5.75</v>
       </c>
       <c r="AC7" s="3" t="n">
         <v>45967.4375</v>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1310,81 +1310,81 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC9" s="3" t="n">
         <v>45967.45833333334</v>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1534,59 +1534,59 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AC11" s="3" t="n">
         <v>45967.45833333334</v>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2127,63 +2127,63 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
         <v>3.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
         <v>1.43</v>
       </c>
       <c r="U17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="W17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X17" t="n">
         <v>2.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
         <v>1.3</v>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2320,81 +2320,81 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.18</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB19" t="n">
         <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.3</v>
       </c>
       <c r="AC19" s="3" t="n">
         <v>45967.60416666666</v>
@@ -2421,81 +2421,81 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="M20" t="n">
-        <v>4.55</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.92</v>
+        <v>2.72</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.2</v>
+        <v>3.86</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="V20" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="W20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.75</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" s="3" t="n">
         <v>45967.60416666666</v>
@@ -2649,49 +2649,49 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.56</v>
+        <v>2.87</v>
       </c>
       <c r="M22" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.66</v>
+        <v>3.76</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
         <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
         <v>3.24</v>
       </c>
       <c r="T22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U22" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="W22" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="X22" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AA22" t="n">
         <v>2.1</v>
